--- a/ig/DM-OCTOBRE-2026/CodeSystem-tre-r392-type-act-smsse-regulee.xlsx
+++ b/ig/DM-OCTOBRE-2026/CodeSystem-tre-r392-type-act-smsse-regulee.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/example/CodeSystem/tre-r392-type-act-smsse-regulee</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r392-type-act-smsse-regulee</t>
   </si>
   <si>
     <t>Identifier</t>

--- a/ig/DM-OCTOBRE-2026/CodeSystem-tre-r392-type-act-smsse-regulee.xlsx
+++ b/ig/DM-OCTOBRE-2026/CodeSystem-tre-r392-type-act-smsse-regulee.xlsx
@@ -334,31 +334,31 @@
     <t>Propriété permettant de renseigner les activitées d'enseignement régulées associées aux types d'activité</t>
   </si>
   <si>
-    <t>activiteReconnaisanceEcars</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#activiteReconnaisanceEcars</t>
+    <t>activiteReconnaisanceContractuelle</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#activiteReconnaisanceContractuelle</t>
   </si>
   <si>
     <t>Propriété permettant de renseigner les activités soumises à reconnaissances (ASR)</t>
   </si>
   <si>
-    <t>modaliteEcars</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#modaliteEcars</t>
-  </si>
-  <si>
-    <t>Propriété permettant de renseigner les modalités des activités autorisées /exercées provenant d'E-CARS</t>
-  </si>
-  <si>
-    <t>formeEcars</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#formeEcars</t>
-  </si>
-  <si>
-    <t>Propriété permettant de renseigner les formes des activités autorisées /exercées provenant d'E-CARS</t>
+    <t>modaliteReconnaissanceContractuelle</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#modaliteReconnaissanceContractuelle</t>
+  </si>
+  <si>
+    <t>Propriété permettant de renseigner les modalités des activités autorisées /exercées provenant provenant d'E-CARS</t>
+  </si>
+  <si>
+    <t>formeReconnaissanceContractuelle</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#formeReconnaissanceContractuelle</t>
+  </si>
+  <si>
+    <t>Propriété permettant de renseigner les formes des activités autorisées /exercées provenant provenant d'E-CARS</t>
   </si>
   <si>
     <t>Level</t>

--- a/ig/DM-OCTOBRE-2026/CodeSystem-tre-r392-type-act-smsse-regulee.xlsx
+++ b/ig/DM-OCTOBRE-2026/CodeSystem-tre-r392-type-act-smsse-regulee.xlsx
@@ -334,10 +334,10 @@
     <t>Propriété permettant de renseigner les activitées d'enseignement régulées associées aux types d'activité</t>
   </si>
   <si>
-    <t>activiteReconnaisanceContractuelle</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#activiteReconnaisanceContractuelle</t>
+    <t>activiteReconnaissanceContractuelle</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#activiteReconnaissanceContractuelle</t>
   </si>
   <si>
     <t>Propriété permettant de renseigner les activités soumises à reconnaissances (ASR)</t>
